--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,55 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111352133</v>
+        <v>137427871</v>
       </c>
       <c r="B2" t="n">
-        <v>91375</v>
+        <v>87481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>720</v>
+        <v>445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrskedika , Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>683516</v>
+        <v>683437</v>
       </c>
       <c r="R2" t="n">
-        <v>6687964</v>
+        <v>6687987</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,72 +759,78 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nina Olsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nina Olsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111352133</t>
+          <t>https://artportalen.se/Sighting/137427871</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112834202</v>
+        <v>111352133</v>
       </c>
       <c r="B3" t="n">
-        <v>93189</v>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrskedika, norr om Granlidens naturreservat, Upl</t>
+          <t>Norrskedika , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>683234</v>
+        <v>683516</v>
       </c>
       <c r="R3" t="n">
-        <v>6687880</v>
+        <v>6687964</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-14</t>
+          <t>2023-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +878,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Larsson</t>
+          <t>Nina Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
+          <t>Nina Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112834202</t>
+          <t>https://artportalen.se/Sighting/111352133</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103023</v>
+        <v>137426260</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,37 +913,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>683556</v>
+        <v>683530</v>
       </c>
       <c r="R4" t="n">
-        <v>6687968</v>
+        <v>6687959</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,49 +987,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103023</t>
+          <t>https://artportalen.se/Sighting/137426260</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112834209</v>
+        <v>112834202</v>
       </c>
       <c r="B5" t="n">
-        <v>99096</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>683570</v>
+        <v>683234</v>
       </c>
       <c r="R5" t="n">
-        <v>6687957</v>
+        <v>6687880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,16 +1104,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112834209</t>
+          <t>https://artportalen.se/Sighting/112834202</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127102827</v>
+        <v>137427145</v>
       </c>
       <c r="B6" t="n">
-        <v>99096</v>
+        <v>93152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1121,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>683523</v>
+        <v>683538</v>
       </c>
       <c r="R6" t="n">
-        <v>6687960</v>
+        <v>6688028</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1175,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,74 +1195,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127102827</t>
+          <t>https://artportalen.se/Sighting/137427145</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127102872</v>
+        <v>137427342</v>
       </c>
       <c r="B7" t="n">
-        <v>99096</v>
+        <v>93517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>683545</v>
+        <v>683539</v>
       </c>
       <c r="R7" t="n">
-        <v>6687974</v>
+        <v>6688030</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,12 +1277,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,27 +1297,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127102872</t>
+          <t>https://artportalen.se/Sighting/137427342</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103076</v>
+        <v>127103023</v>
       </c>
       <c r="B8" t="n">
-        <v>99096</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,7 +1349,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>683546</v>
+        <v>683556</v>
       </c>
       <c r="R8" t="n">
         <v>6687968</v>
@@ -1423,13 +1410,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103076</t>
+          <t>https://artportalen.se/Sighting/127103023</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103104</v>
+        <v>112834209</v>
       </c>
       <c r="B9" t="n">
         <v>99096</v>
@@ -1460,17 +1447,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Norrskedika, norr om Granlidens naturreservat, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>683527</v>
+        <v>683570</v>
       </c>
       <c r="R9" t="n">
-        <v>6687975</v>
+        <v>6687957</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1494,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,24 +1501,28 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Elin Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103104</t>
+          <t>https://artportalen.se/Sighting/112834209</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127103562</v>
+        <v>127102827</v>
       </c>
       <c r="B10" t="n">
         <v>99096</v>
@@ -1566,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>683478</v>
+        <v>683523</v>
       </c>
       <c r="R10" t="n">
-        <v>6688036</v>
+        <v>6687960</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1627,16 +1618,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103562</t>
+          <t>https://artportalen.se/Sighting/127102827</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127102929</v>
+        <v>127102872</v>
       </c>
       <c r="B11" t="n">
-        <v>99142</v>
+        <v>99096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,34 +1635,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Igelsjö, Igelsjö, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>683548</v>
+        <v>683545</v>
       </c>
       <c r="R11" t="n">
-        <v>6687980</v>
+        <v>6687974</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1729,38 +1729,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127102929</t>
+          <t>https://artportalen.se/Sighting/127102872</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127102609</v>
+        <v>127103076</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>683424</v>
+        <v>683546</v>
       </c>
       <c r="R12" t="n">
-        <v>6687976</v>
+        <v>6687968</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1831,38 +1831,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127102609</t>
+          <t>https://artportalen.se/Sighting/127103076</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127103201</v>
+        <v>127103104</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>99096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>683529</v>
+        <v>683527</v>
       </c>
       <c r="R13" t="n">
-        <v>6687992</v>
+        <v>6687975</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1933,38 +1933,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103201</t>
+          <t>https://artportalen.se/Sighting/127103104</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127103294</v>
+        <v>127103562</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>99096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>683498</v>
+        <v>683478</v>
       </c>
       <c r="R14" t="n">
-        <v>6687961</v>
+        <v>6688036</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2035,51 +2035,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103294</t>
+          <t>https://artportalen.se/Sighting/127103562</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127103342</v>
+        <v>137426240</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>99408</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>683494</v>
+        <v>683530</v>
       </c>
       <c r="R15" t="n">
-        <v>6687970</v>
+        <v>6687948</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,65 +2126,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103342</t>
+          <t>https://artportalen.se/Sighting/137426240</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127103351</v>
+        <v>137426444</v>
       </c>
       <c r="B16" t="n">
-        <v>99118</v>
+        <v>99408</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>683491</v>
+        <v>683520</v>
       </c>
       <c r="R16" t="n">
-        <v>6687978</v>
+        <v>6688014</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2228,65 +2228,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103351</t>
+          <t>https://artportalen.se/Sighting/137426444</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127103375</v>
+        <v>137426704</v>
       </c>
       <c r="B17" t="n">
-        <v>99118</v>
+        <v>99408</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>683487</v>
+        <v>683573</v>
       </c>
       <c r="R17" t="n">
-        <v>6687976</v>
+        <v>6688009</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2310,12 +2310,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,65 +2330,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103375</t>
+          <t>https://artportalen.se/Sighting/137426704</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127103414</v>
+        <v>137427110</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>99408</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>683477</v>
+        <v>683562</v>
       </c>
       <c r="R18" t="n">
-        <v>6687996</v>
+        <v>6688020</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,65 +2432,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103414</t>
+          <t>https://artportalen.se/Sighting/137427110</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127103471</v>
+        <v>137427527</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>99408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>683469</v>
+        <v>683497</v>
       </c>
       <c r="R19" t="n">
-        <v>6687995</v>
+        <v>6688054</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2534,49 +2534,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103471</t>
+          <t>https://artportalen.se/Sighting/137427527</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127103504</v>
+        <v>127102929</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99142</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>683476</v>
+        <v>683548</v>
       </c>
       <c r="R20" t="n">
-        <v>6688014</v>
+        <v>6687980</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2647,54 +2647,54 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103504</t>
+          <t>https://artportalen.se/Sighting/127102929</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127103523</v>
+        <v>137426629</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>683503</v>
+        <v>683559</v>
       </c>
       <c r="R21" t="n">
-        <v>6687998</v>
+        <v>6688004</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,65 +2738,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103523</t>
+          <t>https://artportalen.se/Sighting/137426629</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127103541</v>
+        <v>137425991</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>111426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Igelsjö, Igelsjö, Upl</t>
+          <t>Gustavsberg, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>683489</v>
+        <v>683474</v>
       </c>
       <c r="R22" t="n">
-        <v>6688011</v>
+        <v>6687954</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,24 +2840,24 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103541</t>
+          <t>https://artportalen.se/Sighting/137425991</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103575</v>
+        <v>127102609</v>
       </c>
       <c r="B23" t="n">
         <v>99118</v>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>683479</v>
+        <v>683424</v>
       </c>
       <c r="R23" t="n">
-        <v>6688009</v>
+        <v>6687976</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2953,13 +2953,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127103575</t>
+          <t>https://artportalen.se/Sighting/127102609</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103616</v>
+        <v>127103201</v>
       </c>
       <c r="B24" t="n">
         <v>99118</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>683466</v>
+        <v>683529</v>
       </c>
       <c r="R24" t="n">
-        <v>6688023</v>
+        <v>6687992</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3055,7 +3055,1537 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/127103201</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127103294</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>683498</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6687961</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103294</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127103342</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>683494</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6687970</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103342</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127103351</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>683491</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6687978</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103351</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127103375</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>683487</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6687976</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103375</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127103414</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>683477</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6687996</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103414</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127103471</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>683469</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6687995</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103471</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127103504</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>683476</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6688014</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103504</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127103523</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>683503</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6687998</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103523</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127103541</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>683489</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6688011</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103541</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127103575</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>683479</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6688009</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127103575</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127103616</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Igelsjö, Igelsjö, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>683466</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6688023</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/127103616</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137426395</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gustavsberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>683514</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6687960</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426395</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137427979</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99430</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gustavsberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>683456</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6688007</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137427979</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137426450</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98292</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Gustavsberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>683528</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6687997</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426450</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137426083</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101646</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gustavsberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>683519</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6687951</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426083</t>
         </is>
       </c>
     </row>
@@ -3084,6 +4614,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427871</v>
       </c>
       <c r="B2" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137426260</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137427145</v>
       </c>
       <c r="B6" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>137427342</v>
       </c>
       <c r="B7" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137426240</v>
       </c>
       <c r="B15" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>137426444</v>
       </c>
       <c r="B16" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137426704</v>
       </c>
       <c r="B17" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>137427110</v>
       </c>
       <c r="B18" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>137427527</v>
       </c>
       <c r="B19" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137426629</v>
       </c>
       <c r="B21" t="n">
-        <v>99769</v>
+        <v>99770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>137425991</v>
       </c>
       <c r="B22" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>137426395</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137427979</v>
       </c>
       <c r="B37" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137426450</v>
       </c>
       <c r="B38" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137426083</v>
       </c>
       <c r="B39" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427871</v>
       </c>
       <c r="B2" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137426260</v>
       </c>
       <c r="B4" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137427145</v>
       </c>
       <c r="B6" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>137427342</v>
       </c>
       <c r="B7" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137426240</v>
       </c>
       <c r="B15" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>137426444</v>
       </c>
       <c r="B16" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137426704</v>
       </c>
       <c r="B17" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>137427110</v>
       </c>
       <c r="B18" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>137427527</v>
       </c>
       <c r="B19" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137426629</v>
       </c>
       <c r="B21" t="n">
-        <v>99770</v>
+        <v>99773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>137425991</v>
       </c>
       <c r="B22" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>137426395</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137427979</v>
       </c>
       <c r="B37" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137426450</v>
       </c>
       <c r="B38" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137426083</v>
       </c>
       <c r="B39" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 55492-2023 artfynd.xlsx
+++ b/artfynd/A 55492-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427871</v>
       </c>
       <c r="B2" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>137426260</v>
       </c>
       <c r="B4" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137427145</v>
       </c>
       <c r="B6" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>137427342</v>
       </c>
       <c r="B7" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137426240</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>137426444</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>137426704</v>
       </c>
       <c r="B17" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>137427110</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>137427527</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>137426629</v>
       </c>
       <c r="B21" t="n">
-        <v>99773</v>
+        <v>99777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>137425991</v>
       </c>
       <c r="B22" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>137426395</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         <v>137427979</v>
       </c>
       <c r="B37" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>137426450</v>
       </c>
       <c r="B38" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4492,7 +4492,7 @@
         <v>137426083</v>
       </c>
       <c r="B39" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
